--- a/data/Arrivals.XLSX
+++ b/data/Arrivals.XLSX
@@ -500,7 +500,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ООО SAVII PHARM</t>
+          <t>ООО Pharmacy</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
